--- a/AI performance.xlsx
+++ b/AI performance.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonas\iCloudDrive\Cand.Merc BI\Speciale\AI performance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonas\OneDrive\Desktop\Stock predictor project V2\Carbohydrate-Estimation-for-Diabetes-management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592C24C9-2CF6-4E2B-B96F-DB7399342AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DCABC57-FB7A-4356-8AF3-35DCB011870D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{034F3671-DC65-4666-A437-E697FF2F8604}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="518">
   <si>
     <t>dish_id</t>
   </si>
@@ -1615,9 +1615,6 @@
   </si>
   <si>
     <t>MAE</t>
-  </si>
-  <si>
-    <t>PMAE</t>
   </si>
   <si>
     <t>OPEN AI</t>
@@ -1686,7 +1683,8 @@
   </cellStyles>
   <dxfs count="5">
     <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <numFmt numFmtId="164" formatCode="#,##0.000"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -1695,8 +1693,7 @@
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.000"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1737,10 +1734,10 @@
   <autoFilter ref="A1:E508" xr:uid="{BEFCB08C-5DE3-4884-8AC0-BC47A7AA905B}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{68B708C6-B04B-405F-ACF6-0016C449E956}" uniqueName="1" name="dish_id" queryTableFieldId="1" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{7B6B20B3-E1B2-4353-A8B9-A8B1B63EC4C9}" uniqueName="2" name="OPEN AI ESTIMATION" queryTableFieldId="2" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{85F92EDB-640F-43BA-B1A7-CB2F09C265E5}" uniqueName="6" name="CLAUDE ESTIMATION (HAIKU 4.5)" queryTableFieldId="6" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{7B6B20B3-E1B2-4353-A8B9-A8B1B63EC4C9}" uniqueName="2" name="OPEN AI ESTIMATION" queryTableFieldId="2" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{85F92EDB-640F-43BA-B1A7-CB2F09C265E5}" uniqueName="6" name="CLAUDE ESTIMATION (HAIKU 4.5)" queryTableFieldId="6" dataDxfId="2"/>
     <tableColumn id="5" xr3:uid="{B7EB61EC-339F-4006-9674-5A31787BD10D}" uniqueName="5" name="GEMINI ESTIMATION" queryTableFieldId="5" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{20907901-6D74-4B9C-8E61-7D63CF499B0A}" uniqueName="9" name="ACTUAL" queryTableFieldId="9" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{20907901-6D74-4B9C-8E61-7D63CF499B0A}" uniqueName="9" name="ACTUAL" queryTableFieldId="9" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2081,7 +2078,7 @@
         <v>508</v>
       </c>
       <c r="C1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D1" t="s">
         <v>509</v>
@@ -2090,13 +2087,13 @@
         <v>510</v>
       </c>
       <c r="H1" t="s">
+        <v>514</v>
+      </c>
+      <c r="I1" t="s">
         <v>515</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>516</v>
-      </c>
-      <c r="J1" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -2182,7 +2179,18 @@
       <c r="G4" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="H4" s="1"/>
+      <c r="H4" s="1" cm="1">
+        <f t="array" ref="H4">AVERAGE(ABS(dish_carb_split_metadata__1[OPEN AI ESTIMATION]-dish_carb_split_metadata__1[ACTUAL]))</f>
+        <v>6.7807998082840264</v>
+      </c>
+      <c r="I4" s="1" cm="1">
+        <f t="array" ref="I4">AVERAGE(ABS(dish_carb_split_metadata__1[CLAUDE ESTIMATION (HAIKU 4.5)]-dish_carb_split_metadata__1[ACTUAL]))</f>
+        <v>9.4832572485207187</v>
+      </c>
+      <c r="J4" s="1" cm="1">
+        <f t="array" ref="J4">AVERAGE(ABS(dish_carb_split_metadata__1[GEMINI ESTIMATION]-dish_carb_split_metadata__1[ACTUAL]))</f>
+        <v>7.7667879660749541</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -2200,9 +2208,7 @@
       <c r="E5" s="2">
         <v>3.85</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>514</v>
-      </c>
+      <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
